--- a/cv/cv_data.xlsx
+++ b/cv/cv_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\usc.internal\usc\studenthome\r_r113\Documents\GitHubRepo\GitHub\RobinERowland.github.io\cv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsqua\Documents\GitHub\GithubRepo\robinerowland.github.io\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305F4627-6A3B-4B88-B8F7-CCCEC4D2BD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B23CEE-A600-450B-94C7-C31987FB1E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="2628" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="203">
   <si>
     <t>cv_data.xlsx - how this works</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>Best Student Poster</t>
+  </si>
+  <si>
+    <t>Introduction to Scientific Writing</t>
   </si>
 </sst>
 </file>
@@ -739,8 +742,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="17" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1044,8 +1047,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1060,7 +1063,7 @@
     <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -1098,64 +1101,64 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="13">
-        <v>45474</v>
+        <v>81</v>
+      </c>
+      <c r="B2" s="14">
+        <v>45505</v>
       </c>
       <c r="C2" s="11"/>
-      <c r="D2" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>200</v>
-      </c>
+      <c r="D2" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="13"/>
       <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="G2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="10"/>
       <c r="I2" s="10"/>
-      <c r="J2" s="14" t="s">
-        <v>201</v>
-      </c>
+      <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
     </row>
-    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="B3" s="14">
+        <v>45474</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>153</v>
+      <c r="B4" s="5">
+        <v>2026</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1163,162 +1166,158 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="5">
-        <v>2023</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="B5" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="5"/>
       <c r="D5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>157</v>
+      <c r="B6" s="5">
+        <v>2023</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="5">
-        <v>2019</v>
+      <c r="B7" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B8" s="5">
-        <v>2023</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2026</v>
+        <v>2019</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="9" t="s">
-        <v>192</v>
-      </c>
+      <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B9" s="5">
-        <v>2025</v>
-      </c>
-      <c r="C9" s="5"/>
+        <v>2023</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2026</v>
+      </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>154</v>
+      <c r="B10" s="5">
+        <v>2025</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>69</v>
@@ -1326,51 +1325,51 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>66</v>
@@ -1378,25 +1377,25 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>66</v>
@@ -1404,7 +1403,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>63</v>
       </c>
@@ -1413,7 +1412,7 @@
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>77</v>
@@ -1422,7 +1421,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>66</v>
@@ -1430,25 +1429,25 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>66</v>
@@ -1456,43 +1455,47 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>159</v>
+        <v>63</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="I16" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="3" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -1500,21 +1503,21 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="3" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -1522,16 +1525,16 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1544,43 +1547,41 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C20" s="5"/>
-      <c r="D20" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="D20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>88</v>
-      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -1592,19 +1593,19 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1616,19 +1617,19 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="8" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -1640,7 +1641,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -1649,7 +1650,7 @@
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="8" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>91</v>
@@ -1664,19 +1665,19 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1688,19 +1689,19 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1712,7 +1713,7 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
-    <row r="27" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
         <v>35</v>
       </c>
@@ -1721,36 +1722,34 @@
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I27" s="3"/>
-      <c r="J27" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="8" t="s">
         <v>191</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -1758,47 +1757,49 @@
         <v>95</v>
       </c>
       <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C29" s="5"/>
-      <c r="D29" s="3" t="s">
-        <v>98</v>
+      <c r="D29" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A30" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -1810,19 +1811,19 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1834,19 +1835,19 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -1858,91 +1859,93 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
+      <c r="H35" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A36" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -1952,43 +1955,41 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A37" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="3" t="s">
-        <v>118</v>
-      </c>
+      <c r="K37" s="3"/>
       <c r="L37" s="3"/>
     </row>
-    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A38" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -1996,23 +1997,23 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A39" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -2020,79 +2021,81 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="K41" s="3"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A42" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
+      <c r="K42" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A43" s="3" t="s">
         <v>130</v>
       </c>
@@ -2101,10 +2104,10 @@
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2114,19 +2117,19 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A44" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2136,19 +2139,19 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2158,7 +2161,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A46" s="3" t="s">
         <v>130</v>
       </c>
@@ -2167,10 +2170,10 @@
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -2180,19 +2183,19 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -2202,19 +2205,19 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A48" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -2224,7 +2227,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A49" s="3" t="s">
         <v>130</v>
       </c>
@@ -2233,10 +2236,10 @@
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2246,19 +2249,19 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2268,19 +2271,19 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2290,19 +2293,19 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -2312,19 +2315,19 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A53" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -2333,6 +2336,28 @@
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A54" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2343,14 +2368,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -2361,7 +2386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -2372,7 +2397,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2383,7 +2408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
@@ -2394,7 +2419,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -2405,7 +2430,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -2416,7 +2441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -2427,7 +2452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -2438,7 +2463,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
@@ -2449,7 +2474,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
@@ -2460,7 +2485,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -2471,7 +2496,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
@@ -2482,7 +2507,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
@@ -2501,77 +2526,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>13</v>
       </c>

--- a/cv/cv_data.xlsx
+++ b/cv/cv_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsqua\Documents\GitHub\GithubRepo\robinerowland.github.io\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B23CEE-A600-450B-94C7-C31987FB1E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C651956-D54F-4637-8AC4-8A9A9EDC6296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="2628" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="3" r:id="rId1"/>
@@ -1052,7 +1052,7 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.46484375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
@@ -1206,11 +1206,10 @@
       <c r="D6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
@@ -1219,7 +1218,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
@@ -1232,11 +1231,10 @@
       <c r="D7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
@@ -1258,11 +1256,10 @@
       <c r="D8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">

--- a/cv/cv_data.xlsx
+++ b/cv/cv_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rsqua\Documents\GitHub\GithubRepo\robinerowland.github.io\cv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\usc.internal\usc\studenthome\r_r113\Documents\GitHubRepo\GitHub\RobinERowland.github.io\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C651956-D54F-4637-8AC4-8A9A9EDC6296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B6E7BB-8B55-4B38-A2DD-7FF83525C115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="202">
   <si>
     <t>cv_data.xlsx - how this works</t>
   </si>
@@ -552,9 +552,6 @@
   </si>
   <si>
     <t>28-Jan-2026</t>
-  </si>
-  <si>
-    <t>25-Jan-2026</t>
   </si>
   <si>
     <t>28-Aug-2024</t>
@@ -1048,11 +1045,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="8.46484375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
@@ -1063,7 +1060,7 @@
     <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -1101,16 +1098,16 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="14">
-        <v>45505</v>
+        <v>46235</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="10"/>
@@ -1123,7 +1120,7 @@
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
     </row>
-    <row r="3" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>35</v>
       </c>
@@ -1132,10 +1129,10 @@
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -1144,12 +1141,12 @@
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="10"/>
     </row>
-    <row r="4" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
@@ -1171,7 +1168,7 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
@@ -1193,7 +1190,7 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
@@ -1218,7 +1215,7 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
@@ -1243,7 +1240,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>48</v>
       </c>
@@ -1268,7 +1265,7 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1288,7 +1285,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>66</v>
@@ -1296,7 +1293,7 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
@@ -1314,7 +1311,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>69</v>
@@ -1322,7 +1319,7 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
@@ -1340,7 +1337,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>69</v>
@@ -1348,7 +1345,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>63</v>
       </c>
@@ -1366,7 +1363,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>66</v>
@@ -1374,7 +1371,7 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
@@ -1392,7 +1389,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>66</v>
@@ -1400,7 +1397,7 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>63</v>
       </c>
@@ -1418,7 +1415,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>66</v>
@@ -1426,7 +1423,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>63</v>
       </c>
@@ -1444,7 +1441,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>66</v>
@@ -1452,7 +1449,7 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>63</v>
       </c>
@@ -1470,7 +1467,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>66</v>
@@ -1478,7 +1475,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>81</v>
       </c>
@@ -1500,7 +1497,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
@@ -1522,7 +1519,7 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>81</v>
       </c>
@@ -1544,7 +1541,7 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>81</v>
       </c>
@@ -1566,7 +1563,7 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
@@ -1575,7 +1572,7 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>87</v>
@@ -1590,7 +1587,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
@@ -1599,7 +1596,7 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>89</v>
@@ -1614,7 +1611,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
@@ -1623,7 +1620,7 @@
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>90</v>
@@ -1638,7 +1635,7 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
@@ -1662,7 +1659,7 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
@@ -1671,7 +1668,7 @@
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>91</v>
@@ -1686,7 +1683,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
@@ -1695,7 +1692,7 @@
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>92</v>
@@ -1710,7 +1707,7 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
-    <row r="27" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>35</v>
       </c>
@@ -1719,7 +1716,7 @@
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>93</v>
@@ -1734,7 +1731,7 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>35</v>
       </c>
@@ -1743,7 +1740,7 @@
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>94</v>
@@ -1760,7 +1757,7 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
@@ -1769,7 +1766,7 @@
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>97</v>
@@ -1784,7 +1781,7 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>35</v>
       </c>
@@ -1808,7 +1805,7 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>35</v>
       </c>
@@ -1832,7 +1829,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
@@ -1856,7 +1853,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
@@ -1880,7 +1877,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>35</v>
       </c>
@@ -1904,7 +1901,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
@@ -1930,7 +1927,7 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>111</v>
       </c>
@@ -1952,12 +1949,12 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>175</v>
+      <c r="B37" s="4">
+        <v>46047</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="3" t="s">
@@ -1974,12 +1971,12 @@
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
     </row>
-    <row r="38" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="3" t="s">
@@ -1998,12 +1995,12 @@
       </c>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="3" t="s">
@@ -2022,12 +2019,12 @@
       </c>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" spans="1:12" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="3" t="s">
@@ -2046,12 +2043,12 @@
       </c>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="3" t="s">
@@ -2068,12 +2065,12 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="42" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="3" t="s">
@@ -2092,12 +2089,12 @@
       </c>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="3" t="s">
@@ -2114,12 +2111,12 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="3" t="s">
@@ -2136,7 +2133,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>130</v>
       </c>
@@ -2158,7 +2155,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>130</v>
       </c>
@@ -2180,7 +2177,7 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>130</v>
       </c>
@@ -2202,12 +2199,12 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="3" t="s">
@@ -2224,7 +2221,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>130</v>
       </c>
@@ -2246,7 +2243,7 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -2268,7 +2265,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
@@ -2290,12 +2287,12 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="3" t="s">
@@ -2312,7 +2309,7 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>130</v>
       </c>
@@ -2334,12 +2331,12 @@
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="3" t="s">
@@ -2365,14 +2362,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -2383,7 +2380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -2394,7 +2391,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2405,7 +2402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
@@ -2416,7 +2413,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -2427,7 +2424,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -2438,7 +2435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -2449,7 +2446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -2460,7 +2457,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
@@ -2471,7 +2468,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
@@ -2482,7 +2479,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -2493,7 +2490,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>43</v>
       </c>
@@ -2504,7 +2501,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
@@ -2523,77 +2520,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
